--- a/eop-summary.xlsx
+++ b/eop-summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Customer_Freeze\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Churn_Monitoring_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73ED5409-6824-4979-805F-7B648311D6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2004FB2F-5167-4417-8754-B38BC45C31BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E28037BB-DF30-4EC9-BB18-8230C34EC2B8}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="145">
   <si>
     <t>REGIONAL 1</t>
   </si>
@@ -473,6 +473,9 @@
   </si>
   <si>
     <t>1 GBPS</t>
+  </si>
+  <si>
+    <t>Apr</t>
   </si>
 </sst>
 </file>
@@ -860,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D6C85BC-B3BC-48F3-9105-76B4ECBACCE9}">
-  <dimension ref="A1:E308"/>
+  <dimension ref="A1:E410"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -6110,6 +6113,1740 @@
         <v>56</v>
       </c>
     </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B309" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E309" s="1">
+        <v>2761</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E310" s="1">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E311" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A312" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E312" s="1">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A313" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E313" s="1">
+        <v>2787</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C314" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E314" s="1">
+        <v>6938</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E315" s="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A316" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E316" s="1">
+        <v>42386</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A317" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E317" s="1">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E318" s="1">
+        <v>31888</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A319" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E319" s="1">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A320" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E320" s="1">
+        <v>26140</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A321" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E321" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E322" s="1">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E323" s="1">
+        <v>30809</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A324" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E324" s="1">
+        <v>9780</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E325" s="1">
+        <v>22269</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A326" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E326" s="1">
+        <v>13452</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A327" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E327" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A328" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E328" s="1">
+        <v>33668</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A329" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E329" s="1">
+        <v>4594</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A330" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E330" s="1">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A331" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E331" s="1">
+        <v>7231</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A332" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E332" s="1">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A333" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E333" s="1">
+        <v>5519</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E334" s="1">
+        <v>3587</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E335" s="1">
+        <v>6094</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A336" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E336" s="1">
+        <v>4902</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A337" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E337" s="1">
+        <v>4998</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E338" s="1">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E339" s="1">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E340" s="1">
+        <v>15191</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E341" s="1">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A342" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E342" s="1">
+        <v>8964</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A343" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E343" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A344" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E344" s="1">
+        <v>27055</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A345" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B345" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E345" s="1">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A346" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B346" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E346" s="1">
+        <v>6550</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A347" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E347" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A348" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E348" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A349" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C349" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D349" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E349" s="1">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A350" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D350" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E350" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A351" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E351" s="1">
+        <v>3327</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A352" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E352" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A353" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E353" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E354" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E355" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E356" s="1">
+        <v>7457</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E357" s="1">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A358" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E358" s="1">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A359" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E359" s="1">
+        <v>22844</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A360" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C360" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D360" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E360" s="1">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A361" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B361" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C361" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E361" s="1">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A362" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B362" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C362" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E362" s="1">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A363" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B363" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E363" s="1">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A364" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B364" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E364" s="1">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A365" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B365" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C365" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D365" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E365" s="1">
+        <v>3355</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A366" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B366" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E366" s="1">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A367" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E367" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A368" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E368" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A369" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E369" s="1">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A370" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B370" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E370" s="1">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A371" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B371" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E371" s="1">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A372" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D372" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E372" s="1">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A373" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B373" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D373" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E373" s="1">
+        <v>6839</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A374" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D374" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E374" s="1">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A375" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D375" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E375" s="1">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A376" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D376" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E376" s="1">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A377" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D377" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E377" s="1">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A378" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E378" s="1">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A379" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B379" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C379" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D379" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E379" s="1">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A380" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B380" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C380" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D380" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E380" s="1">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A381" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B381" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C381" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D381" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E381" s="1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A382" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B382" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C382" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D382" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E382" s="1">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A383" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B383" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C383" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D383" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E383" s="1">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A384" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B384" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C384" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D384" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E384" s="1">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A385" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B385" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C385" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D385" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E385" s="1">
+        <v>5107</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A386" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B386" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D386" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E386" s="1">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A387" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D387" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E387" s="1">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A388" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B388" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C388" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D388" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E388" s="1">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A389" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B389" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D389" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E389" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A390" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B390" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C390" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D390" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E390" s="1">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A391" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B391" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C391" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D391" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E391" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A392" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B392" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C392" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D392" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E392" s="1">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A393" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B393" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C393" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D393" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E393" s="1">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A394" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B394" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D394" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E394" s="1">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A395" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E395" s="1">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A396" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D396" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E396" s="1">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A397" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B397" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C397" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D397" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E397" s="1">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A398" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D398" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E398" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A399" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B399" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D399" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E399" s="1">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A400" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B400" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C400" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D400" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E400" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A401" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B401" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C401" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D401" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E401" s="1">
+        <v>18132</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A402" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D402" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E402" s="1">
+        <v>19495</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A403" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B403" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C403" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D403" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E403" s="1">
+        <v>3836</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A404" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B404" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D404" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E404" s="1">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A405" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B405" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C405" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D405" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E405" s="1">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A406" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B406" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C406" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D406" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E406" s="1">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A407" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B407" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D407" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E407" s="1">
+        <v>5671</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A408" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D408" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E408" s="1">
+        <v>4792</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A409" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B409" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D409" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E409" s="1">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A410" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B410" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C410" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D410" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E410" s="1">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6117,7 +7854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91508C2B-BB50-4B90-B35A-4928148A54F5}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
@@ -6664,6 +8401,182 @@
         <v>177</v>
       </c>
     </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C50" s="1">
+        <v>17604</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C51" s="1">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C52" s="1">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C53" s="1">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C54" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C55" s="1">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C56" s="1">
+        <v>192781</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" s="1">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" s="1">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C59" s="1">
+        <v>35773</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C60" s="1">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C61" s="1">
+        <v>211417</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C62" s="1">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C63" s="1">
+        <v>14553</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C64" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C65" s="1">
+        <v>174</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C51">
     <sortCondition ref="A2:A51"/>

--- a/eop-summary.xlsx
+++ b/eop-summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Churn_Monitoring_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2004FB2F-5167-4417-8754-B38BC45C31BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3B33F2-C41C-4480-A4CD-ECBF971E5AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E28037BB-DF30-4EC9-BB18-8230C34EC2B8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{E28037BB-DF30-4EC9-BB18-8230C34EC2B8}"/>
   </bookViews>
   <sheets>
     <sheet name="eop_region" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2212" uniqueCount="146">
   <si>
     <t>REGIONAL 1</t>
   </si>
@@ -476,6 +476,9 @@
   </si>
   <si>
     <t>Apr</t>
+  </si>
+  <si>
+    <t>May</t>
   </si>
 </sst>
 </file>
@@ -526,9 +529,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -863,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D6C85BC-B3BC-48F3-9105-76B4ECBACCE9}">
-  <dimension ref="A1:E410"/>
+  <dimension ref="A1:E512"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -7847,6 +7851,1740 @@
         <v>61</v>
       </c>
     </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A411" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C411" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D411" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E411" s="1">
+        <v>15151</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A412" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B412" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C412" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D412" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E412" s="1">
+        <v>2947</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A413" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B413" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C413" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D413" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E413" s="1">
+        <v>22975</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A414" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B414" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C414" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D414" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E414" s="1">
+        <v>2967</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A415" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B415" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C415" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D415" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E415" s="1">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A416" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B416" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C416" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D416" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E416" s="1">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A417" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B417" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C417" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D417" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E417" s="1">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A418" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C418" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E418" s="1">
+        <v>4042</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A419" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C419" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D419" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E419" s="1">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A420" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C420" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D420" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E420" s="1">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A421" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C421" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D421" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E421" s="1">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A422" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B422" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C422" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D422" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E422" s="1">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A423" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C423" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D423" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E423" s="1">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A424" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B424" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C424" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D424" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E424" s="1">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A425" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B425" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C425" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E425" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A426" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C426" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D426" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E426" s="1">
+        <v>34066</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A427" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B427" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C427" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D427" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E427" s="1">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A428" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B428" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C428" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D428" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E428" s="1">
+        <v>22551</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A429" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B429" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C429" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D429" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E429" s="1">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A430" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B430" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C430" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D430" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E430" s="1">
+        <v>9185</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A431" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B431" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C431" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D431" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E431" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A432" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B432" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C432" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D432" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E432" s="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A433" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B433" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C433" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D433" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E433" s="1">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A434" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B434" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C434" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D434" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E434" s="1">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A435" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B435" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C435" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D435" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E435" s="1">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A436" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B436" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C436" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D436" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E436" s="1">
+        <v>3269</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A437" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C437" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D437" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E437" s="1">
+        <v>32733</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A438" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C438" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D438" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E438" s="1">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A439" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B439" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C439" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D439" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E439" s="1">
+        <v>27052</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A440" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B440" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C440" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D440" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E440" s="1">
+        <v>13402</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A441" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B441" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C441" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D441" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E441" s="1">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A442" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C442" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D442" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E442" s="1">
+        <v>8269</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A443" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B443" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C443" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D443" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E443" s="1">
+        <v>5827</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A444" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B444" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C444" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D444" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E444" s="1">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A445" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C445" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D445" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E445" s="1">
+        <v>4626</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A446" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B446" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C446" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D446" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E446" s="1">
+        <v>6173</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A447" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B447" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C447" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D447" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E447" s="1">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A448" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B448" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C448" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D448" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E448" s="1">
+        <v>4916</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A449" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B449" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C449" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D449" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E449" s="1">
+        <v>7203</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A450" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B450" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C450" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D450" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E450" s="1">
+        <v>4982</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A451" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B451" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C451" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D451" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E451" s="1">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A452" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B452" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C452" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D452" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E452" s="1">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A453" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B453" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C453" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D453" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E453" s="1">
+        <v>5561</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A454" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B454" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C454" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D454" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E454" s="1">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A455" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B455" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C455" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D455" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E455" s="1">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A456" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B456" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C456" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D456" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E456" s="1">
+        <v>6626</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A457" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B457" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C457" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D457" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E457" s="1">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A458" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B458" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C458" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D458" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E458" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A459" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B459" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C459" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D459" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E459" s="1">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A460" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B460" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C460" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D460" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E460" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A461" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B461" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C461" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D461" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E461" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A462" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B462" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C462" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D462" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E462" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A463" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B463" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C463" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D463" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E463" s="1">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A464" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B464" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C464" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D464" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E464" s="1">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A465" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B465" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C465" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D465" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E465" s="1">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A466" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B466" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C466" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D466" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E466" s="1">
+        <v>3487</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A467" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B467" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C467" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D467" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E467" s="1">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A468" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B468" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C468" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D468" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E468" s="1">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A469" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B469" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C469" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D469" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E469" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A470" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B470" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C470" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D470" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E470" s="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A471" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B471" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C471" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D471" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E471" s="1">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A472" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B472" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C472" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D472" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E472" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A473" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B473" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C473" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D473" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E473" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A474" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B474" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C474" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D474" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E474" s="1">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A475" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C475" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D475" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E475" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A476" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B476" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C476" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D476" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E476" s="1">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A477" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C477" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D477" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E477" s="1">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A478" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B478" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C478" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D478" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E478" s="1">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A479" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B479" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C479" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D479" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E479" s="1">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A480" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B480" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C480" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D480" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E480" s="1">
+        <v>4907</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A481" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B481" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C481" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D481" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E481" s="1">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A482" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B482" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C482" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D482" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E482" s="1">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A483" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B483" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C483" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D483" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E483" s="1">
+        <v>26558</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A484" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B484" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C484" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D484" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E484" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A485" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B485" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C485" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D485" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E485" s="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A486" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B486" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C486" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D486" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E486" s="1">
+        <v>42965</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A487" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C487" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D487" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E487" s="1">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A488" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C488" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D488" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E488" s="1">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A489" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C489" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D489" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E489" s="1">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A490" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C490" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D490" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E490" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A491" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B491" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C491" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D491" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E491" s="1">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A492" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C492" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D492" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E492" s="1">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A493" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B493" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C493" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D493" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E493" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A494" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B494" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C494" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D494" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E494" s="1">
+        <v>5207</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A495" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B495" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C495" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D495" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E495" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A496" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B496" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C496" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D496" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E496" s="1">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A497" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B497" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C497" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D497" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E497" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A498" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B498" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C498" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D498" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E498" s="1">
+        <v>18472</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A499" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B499" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C499" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D499" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E499" s="1">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A500" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B500" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C500" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D500" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E500" s="1">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A501" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B501" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C501" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D501" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E501" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A502" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B502" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C502" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D502" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E502" s="1">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A503" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B503" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C503" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D503" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E503" s="1">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A504" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B504" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C504" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D504" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E504" s="1">
+        <v>19863</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A505" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B505" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C505" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D505" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E505" s="1">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A506" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B506" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C506" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D506" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E506" s="1">
+        <v>7553</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A507" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C507" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D507" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E507" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A508" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B508" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C508" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D508" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E508" s="1">
+        <v>31319</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A509" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B509" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C509" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D509" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E509" s="1">
+        <v>9955</v>
+      </c>
+    </row>
+    <row r="510" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A510" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B510" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C510" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D510" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E510" s="1">
+        <v>6770</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A511" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B511" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C511" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D511" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E511" s="1">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="512" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A512" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B512" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C512" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D512" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E512" s="1">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7854,7 +9592,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91508C2B-BB50-4B90-B35A-4928148A54F5}">
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
@@ -8577,6 +10315,182 @@
         <v>174</v>
       </c>
     </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C66" s="1">
+        <v>17616</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C67" s="1">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C68" s="1">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C69" s="1">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C70" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C71" s="1">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C72" s="1">
+        <v>198240</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C73" s="1">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C74" s="1">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C75" s="1">
+        <v>38502</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C76" s="1">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C77" s="1">
+        <v>210484</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C78" s="1">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C79" s="1">
+        <v>14518</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C80" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C81" s="1">
+        <v>166</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C51">
     <sortCondition ref="A2:A51"/>

--- a/eop-summary.xlsx
+++ b/eop-summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Churn_Monitoring_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3B33F2-C41C-4480-A4CD-ECBF971E5AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA49AAE-FE6F-4424-9D28-BAD50A802931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{E28037BB-DF30-4EC9-BB18-8230C34EC2B8}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">eop_product!$A$1:$C$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">eop_region!$A$1:$E$308</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">eop_region!$J$4:$M$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2212" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2628" uniqueCount="147">
   <si>
     <t>REGIONAL 1</t>
   </si>
@@ -479,6 +479,9 @@
   </si>
   <si>
     <t>May</t>
+  </si>
+  <si>
+    <t>Jun</t>
   </si>
 </sst>
 </file>
@@ -529,10 +532,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -867,7 +869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D6C85BC-B3BC-48F3-9105-76B4ECBACCE9}">
-  <dimension ref="A1:E512"/>
+  <dimension ref="A1:E608"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -7852,7 +7854,7 @@
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A411" s="2" t="s">
+      <c r="A411" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B411" s="1" t="s">
@@ -7869,7 +7871,7 @@
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A412" s="2" t="s">
+      <c r="A412" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B412" s="1" t="s">
@@ -7886,7 +7888,7 @@
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A413" s="2" t="s">
+      <c r="A413" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B413" s="1" t="s">
@@ -7903,7 +7905,7 @@
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A414" s="2" t="s">
+      <c r="A414" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B414" s="1" t="s">
@@ -7920,7 +7922,7 @@
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A415" s="2" t="s">
+      <c r="A415" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B415" s="1" t="s">
@@ -7937,7 +7939,7 @@
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A416" s="2" t="s">
+      <c r="A416" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B416" s="1" t="s">
@@ -7954,7 +7956,7 @@
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A417" s="2" t="s">
+      <c r="A417" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B417" s="1" t="s">
@@ -7971,7 +7973,7 @@
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A418" s="2" t="s">
+      <c r="A418" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B418" s="1" t="s">
@@ -7988,7 +7990,7 @@
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A419" s="2" t="s">
+      <c r="A419" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B419" s="1" t="s">
@@ -8005,7 +8007,7 @@
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A420" s="2" t="s">
+      <c r="A420" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B420" s="1" t="s">
@@ -8022,7 +8024,7 @@
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A421" s="2" t="s">
+      <c r="A421" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B421" s="1" t="s">
@@ -8039,7 +8041,7 @@
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A422" s="2" t="s">
+      <c r="A422" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B422" s="1" t="s">
@@ -8056,7 +8058,7 @@
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A423" s="2" t="s">
+      <c r="A423" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B423" s="1" t="s">
@@ -8073,7 +8075,7 @@
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A424" s="2" t="s">
+      <c r="A424" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B424" s="1" t="s">
@@ -8090,7 +8092,7 @@
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A425" s="2" t="s">
+      <c r="A425" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B425" s="1" t="s">
@@ -8107,7 +8109,7 @@
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A426" s="2" t="s">
+      <c r="A426" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B426" s="1" t="s">
@@ -8124,7 +8126,7 @@
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A427" s="2" t="s">
+      <c r="A427" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B427" s="1" t="s">
@@ -8141,7 +8143,7 @@
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A428" s="2" t="s">
+      <c r="A428" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B428" s="1" t="s">
@@ -8158,7 +8160,7 @@
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A429" s="2" t="s">
+      <c r="A429" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B429" s="1" t="s">
@@ -8175,7 +8177,7 @@
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A430" s="2" t="s">
+      <c r="A430" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B430" s="1" t="s">
@@ -8192,7 +8194,7 @@
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A431" s="2" t="s">
+      <c r="A431" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B431" s="1" t="s">
@@ -8209,7 +8211,7 @@
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A432" s="2" t="s">
+      <c r="A432" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B432" s="1" t="s">
@@ -8226,7 +8228,7 @@
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A433" s="2" t="s">
+      <c r="A433" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B433" s="1" t="s">
@@ -8243,7 +8245,7 @@
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A434" s="2" t="s">
+      <c r="A434" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B434" s="1" t="s">
@@ -8260,7 +8262,7 @@
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A435" s="2" t="s">
+      <c r="A435" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B435" s="1" t="s">
@@ -8277,7 +8279,7 @@
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A436" s="2" t="s">
+      <c r="A436" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B436" s="1" t="s">
@@ -8294,7 +8296,7 @@
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A437" s="2" t="s">
+      <c r="A437" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B437" s="1" t="s">
@@ -8311,7 +8313,7 @@
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A438" s="2" t="s">
+      <c r="A438" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B438" s="1" t="s">
@@ -8328,7 +8330,7 @@
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A439" s="2" t="s">
+      <c r="A439" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B439" s="1" t="s">
@@ -8345,7 +8347,7 @@
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A440" s="2" t="s">
+      <c r="A440" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B440" s="1" t="s">
@@ -8362,7 +8364,7 @@
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A441" s="2" t="s">
+      <c r="A441" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B441" s="1" t="s">
@@ -8379,7 +8381,7 @@
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A442" s="2" t="s">
+      <c r="A442" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B442" s="1" t="s">
@@ -8396,7 +8398,7 @@
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A443" s="2" t="s">
+      <c r="A443" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B443" s="1" t="s">
@@ -8413,7 +8415,7 @@
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A444" s="2" t="s">
+      <c r="A444" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B444" s="1" t="s">
@@ -8430,7 +8432,7 @@
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A445" s="2" t="s">
+      <c r="A445" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B445" s="1" t="s">
@@ -8447,7 +8449,7 @@
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A446" s="2" t="s">
+      <c r="A446" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B446" s="1" t="s">
@@ -8464,7 +8466,7 @@
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A447" s="2" t="s">
+      <c r="A447" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B447" s="1" t="s">
@@ -8481,7 +8483,7 @@
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A448" s="2" t="s">
+      <c r="A448" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B448" s="1" t="s">
@@ -8498,7 +8500,7 @@
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A449" s="2" t="s">
+      <c r="A449" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B449" s="1" t="s">
@@ -8515,7 +8517,7 @@
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A450" s="2" t="s">
+      <c r="A450" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B450" s="1" t="s">
@@ -8532,7 +8534,7 @@
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A451" s="2" t="s">
+      <c r="A451" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B451" s="1" t="s">
@@ -8549,7 +8551,7 @@
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A452" s="2" t="s">
+      <c r="A452" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B452" s="1" t="s">
@@ -8566,7 +8568,7 @@
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A453" s="2" t="s">
+      <c r="A453" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B453" s="1" t="s">
@@ -8583,7 +8585,7 @@
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A454" s="2" t="s">
+      <c r="A454" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B454" s="1" t="s">
@@ -8600,7 +8602,7 @@
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A455" s="2" t="s">
+      <c r="A455" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B455" s="1" t="s">
@@ -8617,7 +8619,7 @@
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A456" s="2" t="s">
+      <c r="A456" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B456" s="1" t="s">
@@ -8634,7 +8636,7 @@
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A457" s="2" t="s">
+      <c r="A457" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B457" s="1" t="s">
@@ -8651,7 +8653,7 @@
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A458" s="2" t="s">
+      <c r="A458" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B458" s="1" t="s">
@@ -8668,7 +8670,7 @@
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A459" s="2" t="s">
+      <c r="A459" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B459" s="1" t="s">
@@ -8685,7 +8687,7 @@
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A460" s="2" t="s">
+      <c r="A460" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B460" s="1" t="s">
@@ -8702,7 +8704,7 @@
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A461" s="2" t="s">
+      <c r="A461" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B461" s="1" t="s">
@@ -8719,7 +8721,7 @@
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A462" s="2" t="s">
+      <c r="A462" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B462" s="1" t="s">
@@ -8736,7 +8738,7 @@
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A463" s="2" t="s">
+      <c r="A463" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B463" s="1" t="s">
@@ -8753,7 +8755,7 @@
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A464" s="2" t="s">
+      <c r="A464" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B464" s="1" t="s">
@@ -8770,7 +8772,7 @@
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A465" s="2" t="s">
+      <c r="A465" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B465" s="1" t="s">
@@ -8787,7 +8789,7 @@
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A466" s="2" t="s">
+      <c r="A466" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B466" s="1" t="s">
@@ -8804,7 +8806,7 @@
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A467" s="2" t="s">
+      <c r="A467" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B467" s="1" t="s">
@@ -8821,7 +8823,7 @@
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A468" s="2" t="s">
+      <c r="A468" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B468" s="1" t="s">
@@ -8838,7 +8840,7 @@
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A469" s="2" t="s">
+      <c r="A469" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B469" s="1" t="s">
@@ -8855,7 +8857,7 @@
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A470" s="2" t="s">
+      <c r="A470" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B470" s="1" t="s">
@@ -8872,7 +8874,7 @@
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A471" s="2" t="s">
+      <c r="A471" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B471" s="1" t="s">
@@ -8889,7 +8891,7 @@
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A472" s="2" t="s">
+      <c r="A472" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B472" s="1" t="s">
@@ -8906,7 +8908,7 @@
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A473" s="2" t="s">
+      <c r="A473" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B473" s="1" t="s">
@@ -8923,7 +8925,7 @@
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A474" s="2" t="s">
+      <c r="A474" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B474" s="1" t="s">
@@ -8940,7 +8942,7 @@
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A475" s="2" t="s">
+      <c r="A475" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B475" s="1" t="s">
@@ -8957,7 +8959,7 @@
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A476" s="2" t="s">
+      <c r="A476" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B476" s="1" t="s">
@@ -8974,7 +8976,7 @@
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A477" s="2" t="s">
+      <c r="A477" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B477" s="1" t="s">
@@ -8991,7 +8993,7 @@
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A478" s="2" t="s">
+      <c r="A478" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B478" s="1" t="s">
@@ -9008,7 +9010,7 @@
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A479" s="2" t="s">
+      <c r="A479" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B479" s="1" t="s">
@@ -9025,7 +9027,7 @@
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A480" s="2" t="s">
+      <c r="A480" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B480" s="1" t="s">
@@ -9042,7 +9044,7 @@
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A481" s="2" t="s">
+      <c r="A481" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B481" s="1" t="s">
@@ -9059,7 +9061,7 @@
       </c>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A482" s="2" t="s">
+      <c r="A482" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B482" s="1" t="s">
@@ -9076,7 +9078,7 @@
       </c>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A483" s="2" t="s">
+      <c r="A483" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B483" s="1" t="s">
@@ -9093,7 +9095,7 @@
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A484" s="2" t="s">
+      <c r="A484" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B484" s="1" t="s">
@@ -9110,7 +9112,7 @@
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A485" s="2" t="s">
+      <c r="A485" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B485" s="1" t="s">
@@ -9127,7 +9129,7 @@
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A486" s="2" t="s">
+      <c r="A486" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B486" s="1" t="s">
@@ -9144,7 +9146,7 @@
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A487" s="2" t="s">
+      <c r="A487" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B487" s="1" t="s">
@@ -9161,7 +9163,7 @@
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A488" s="2" t="s">
+      <c r="A488" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B488" s="1" t="s">
@@ -9178,7 +9180,7 @@
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A489" s="2" t="s">
+      <c r="A489" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B489" s="1" t="s">
@@ -9195,7 +9197,7 @@
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A490" s="2" t="s">
+      <c r="A490" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B490" s="1" t="s">
@@ -9212,7 +9214,7 @@
       </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A491" s="2" t="s">
+      <c r="A491" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B491" s="1" t="s">
@@ -9229,7 +9231,7 @@
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A492" s="2" t="s">
+      <c r="A492" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B492" s="1" t="s">
@@ -9246,7 +9248,7 @@
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A493" s="2" t="s">
+      <c r="A493" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B493" s="1" t="s">
@@ -9263,7 +9265,7 @@
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A494" s="2" t="s">
+      <c r="A494" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B494" s="1" t="s">
@@ -9280,7 +9282,7 @@
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A495" s="2" t="s">
+      <c r="A495" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B495" s="1" t="s">
@@ -9297,7 +9299,7 @@
       </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A496" s="2" t="s">
+      <c r="A496" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B496" s="1" t="s">
@@ -9314,7 +9316,7 @@
       </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A497" s="2" t="s">
+      <c r="A497" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B497" s="1" t="s">
@@ -9331,7 +9333,7 @@
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A498" s="2" t="s">
+      <c r="A498" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B498" s="1" t="s">
@@ -9348,7 +9350,7 @@
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A499" s="2" t="s">
+      <c r="A499" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B499" s="1" t="s">
@@ -9365,7 +9367,7 @@
       </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A500" s="2" t="s">
+      <c r="A500" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B500" s="1" t="s">
@@ -9382,7 +9384,7 @@
       </c>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A501" s="2" t="s">
+      <c r="A501" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B501" s="1" t="s">
@@ -9399,7 +9401,7 @@
       </c>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A502" s="2" t="s">
+      <c r="A502" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B502" s="1" t="s">
@@ -9416,7 +9418,7 @@
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A503" s="2" t="s">
+      <c r="A503" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B503" s="1" t="s">
@@ -9433,7 +9435,7 @@
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A504" s="2" t="s">
+      <c r="A504" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B504" s="1" t="s">
@@ -9450,7 +9452,7 @@
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A505" s="2" t="s">
+      <c r="A505" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B505" s="1" t="s">
@@ -9467,7 +9469,7 @@
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A506" s="2" t="s">
+      <c r="A506" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B506" s="1" t="s">
@@ -9484,7 +9486,7 @@
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A507" s="2" t="s">
+      <c r="A507" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B507" s="1" t="s">
@@ -9501,7 +9503,7 @@
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A508" s="2" t="s">
+      <c r="A508" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B508" s="1" t="s">
@@ -9518,7 +9520,7 @@
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A509" s="2" t="s">
+      <c r="A509" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B509" s="1" t="s">
@@ -9535,7 +9537,7 @@
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A510" s="2" t="s">
+      <c r="A510" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B510" s="1" t="s">
@@ -9552,7 +9554,7 @@
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A511" s="2" t="s">
+      <c r="A511" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B511" s="1" t="s">
@@ -9569,7 +9571,7 @@
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A512" s="2" t="s">
+      <c r="A512" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B512" s="1" t="s">
@@ -9585,14 +9587,1649 @@
         <v>3</v>
       </c>
     </row>
+    <row r="513" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A513" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B513" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C513" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D513" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E513" s="1">
+        <v>3127</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A514" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B514" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C514" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D514" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E514" s="1">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A515" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C515" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D515" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E515" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A516" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C516" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D516" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E516" s="1">
+        <v>2801</v>
+      </c>
+    </row>
+    <row r="517" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A517" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C517" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D517" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E517" s="1">
+        <v>3128</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A518" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C518" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D518" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E518" s="1">
+        <v>7465</v>
+      </c>
+    </row>
+    <row r="519" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A519" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C519" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D519" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E519" s="1">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="520" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A520" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C520" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D520" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E520" s="1">
+        <v>43205</v>
+      </c>
+    </row>
+    <row r="521" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A521" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C521" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D521" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E521" s="1">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A522" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C522" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D522" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E522" s="1">
+        <v>33286</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A523" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C523" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D523" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E523" s="1">
+        <v>2804</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A524" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C524" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D524" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E524" s="1">
+        <v>26817</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A525" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C525" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D525" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E525" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A526" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C526" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D526" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E526" s="1">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A527" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C527" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D527" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E527" s="1">
+        <v>30966</v>
+      </c>
+    </row>
+    <row r="528" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A528" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C528" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D528" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E528" s="1">
+        <v>10096</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A529" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C529" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D529" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E529" s="1">
+        <v>22743</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A530" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C530" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D530" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E530" s="1">
+        <v>13230</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A531" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C531" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D531" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E531" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A532" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C532" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D532" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E532" s="1">
+        <v>33979</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A533" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B533" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C533" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D533" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E533" s="1">
+        <v>4670</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A534" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C534" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D534" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E534" s="1">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A535" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C535" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D535" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E535" s="1">
+        <v>7150</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A536" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B536" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C536" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D536" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E536" s="1">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A537" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C537" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D537" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E537" s="1">
+        <v>5605</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A538" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C538" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D538" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E538" s="1">
+        <v>3390</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A539" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B539" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C539" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D539" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E539" s="1">
+        <v>6191</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A540" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C540" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D540" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E540" s="1">
+        <v>4911</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A541" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C541" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D541" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E541" s="1">
+        <v>4976</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A542" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C542" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D542" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E542" s="1">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A543" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C543" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D543" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E543" s="1">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A544" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C544" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D544" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E544" s="1">
+        <v>15047</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A545" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C545" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D545" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E545" s="1">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A546" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C546" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D546" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E546" s="1">
+        <v>9385</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A547" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B547" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C547" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D547" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E547" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A548" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B548" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C548" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D548" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E548" s="1">
+        <v>26902</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A549" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B549" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C549" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D549" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E549" s="1">
+        <v>8241</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A550" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B550" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C550" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D550" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E550" s="1">
+        <v>6659</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A551" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B551" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C551" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D551" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E551" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A552" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B552" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C552" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D552" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E552" s="1">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A553" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B553" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C553" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D553" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E553" s="1">
+        <v>3330</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A554" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C554" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D554" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E554" s="1">
+        <v>7616</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A555" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B555" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C555" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D555" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E555" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A556" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B556" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C556" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D556" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E556" s="1">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A557" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B557" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C557" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D557" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E557" s="1">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A558" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C558" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D558" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E558" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A559" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C559" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D559" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E559" s="1">
+        <v>23080</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A560" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B560" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C560" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D560" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E560" s="1">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A561" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B561" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C561" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D561" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E561" s="1">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A562" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C562" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D562" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E562" s="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="563" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A563" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C563" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D563" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E563" s="1">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="564" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A564" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B564" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C564" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D564" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E564" s="1">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="565" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A565" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C565" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D565" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E565" s="1">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="566" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A566" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C566" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D566" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E566" s="1">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="567" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A567" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C567" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D567" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E567" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="568" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A568" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B568" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C568" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D568" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E568" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="569" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A569" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C569" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D569" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E569" s="1">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="570" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A570" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C570" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D570" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E570" s="1">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="571" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A571" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C571" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D571" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E571" s="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="572" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A572" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C572" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D572" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E572" s="1">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="573" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A573" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C573" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D573" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E573" s="1">
+        <v>6659</v>
+      </c>
+    </row>
+    <row r="574" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A574" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C574" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D574" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E574" s="1">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="575" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A575" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C575" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D575" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E575" s="1">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="576" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A576" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C576" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D576" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E576" s="1">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="577" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A577" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C577" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D577" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E577" s="1">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="578" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A578" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C578" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D578" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E578" s="1">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="579" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A579" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C579" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D579" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E579" s="1">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="580" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A580" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C580" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D580" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E580" s="1">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="581" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A581" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C581" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D581" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E581" s="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="582" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A582" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C582" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D582" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E582" s="1">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="583" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A583" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B583" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C583" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D583" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E583" s="1">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="584" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A584" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C584" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D584" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E584" s="1">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="585" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A585" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B585" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C585" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D585" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E585" s="1">
+        <v>5274</v>
+      </c>
+    </row>
+    <row r="586" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A586" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C586" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D586" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E586" s="1">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="587" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A587" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B587" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C587" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D587" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E587" s="1">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="588" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A588" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C588" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D588" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E588" s="1">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="589" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A589" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B589" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C589" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D589" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E589" s="1">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="590" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A590" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B590" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C590" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D590" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E590" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="591" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A591" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B591" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C591" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D591" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E591" s="1">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="592" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A592" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B592" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C592" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D592" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E592" s="1">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="593" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A593" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B593" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C593" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D593" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E593" s="1">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="594" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A594" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B594" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C594" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D594" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E594" s="1">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="595" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A595" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C595" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D595" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E595" s="1">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="596" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A596" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C596" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D596" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E596" s="1">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="597" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A597" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C597" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D597" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E597" s="1">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="598" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A598" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C598" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D598" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E598" s="1">
+        <v>18782</v>
+      </c>
+    </row>
+    <row r="599" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A599" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C599" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D599" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E599" s="1">
+        <v>20143</v>
+      </c>
+    </row>
+    <row r="600" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A600" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C600" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D600" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E600" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="601" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A601" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C601" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D601" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E601" s="1">
+        <v>4302</v>
+      </c>
+    </row>
+    <row r="602" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A602" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C602" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D602" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E602" s="1">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="603" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A603" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C603" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D603" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E603" s="1">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="604" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A604" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C604" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D604" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E604" s="1">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="605" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A605" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C605" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D605" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E605" s="1">
+        <v>5982</v>
+      </c>
+    </row>
+    <row r="606" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A606" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C606" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D606" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E606" s="1">
+        <v>5050</v>
+      </c>
+    </row>
+    <row r="607" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A607" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C607" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D607" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E607" s="1">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="608" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A608" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C608" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D608" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E608" s="1">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J5:M117">
+    <sortCondition ref="J5:J117"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91508C2B-BB50-4B90-B35A-4928148A54F5}">
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
@@ -10491,6 +12128,182 @@
         <v>166</v>
       </c>
     </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C82" s="1">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C83" s="1">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C84" s="1">
+        <v>202356</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C85" s="1">
+        <v>40812</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C86" s="1">
+        <v>209064</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C87" s="1">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C88" s="1">
+        <v>14405</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C89" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C90" s="1">
+        <v>17555</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C91" s="1">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C92" s="1">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C93" s="1">
+        <v>2636</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C94" s="1">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C95" s="1">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C96" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C97" s="1">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C51">
     <sortCondition ref="A2:A51"/>

--- a/eop-summary.xlsx
+++ b/eop-summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\Churn_Monitoring_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA49AAE-FE6F-4424-9D28-BAD50A802931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A3E063-D8EF-4273-9003-8333A9EC72BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{E28037BB-DF30-4EC9-BB18-8230C34EC2B8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E28037BB-DF30-4EC9-BB18-8230C34EC2B8}"/>
   </bookViews>
   <sheets>
     <sheet name="eop_region" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">eop_product!$A$1:$C$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">eop_region!$J$4:$M$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">eop_region!$A$1:$E$608</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2628" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3044" uniqueCount="148">
   <si>
     <t>REGIONAL 1</t>
   </si>
@@ -482,6 +482,9 @@
   </si>
   <si>
     <t>Jun</t>
+  </si>
+  <si>
+    <t>Jul</t>
   </si>
 </sst>
 </file>
@@ -869,7 +872,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D6C85BC-B3BC-48F3-9105-76B4ECBACCE9}">
-  <dimension ref="A1:E608"/>
+  <dimension ref="A1:E704"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -11219,7 +11222,1640 @@
         <v>69</v>
       </c>
     </row>
+    <row r="609" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A609" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B609" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C609" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D609" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E609" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="610" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A610" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C610" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D610" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E610" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="611" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A611" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C611" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D611" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E611" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="612" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A612" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C612" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D612" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E612" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="613" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A613" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C613" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D613" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E613" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="614" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A614" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C614" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D614" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E614" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="615" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A615" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C615" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D615" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E615" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="616" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A616" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C616" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D616" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E616" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="617" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A617" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C617" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D617" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E617" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="618" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A618" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C618" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D618" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E618" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="619" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A619" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C619" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D619" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E619" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="620" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A620" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C620" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D620" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E620" s="1">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="621" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A621" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C621" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D621" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E621" s="1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="622" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A622" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C622" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D622" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E622" s="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="623" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A623" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C623" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D623" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E623" s="1">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="624" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A624" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C624" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D624" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E624" s="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="625" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A625" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C625" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D625" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E625" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="626" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A626" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C626" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D626" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E626" s="1">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="627" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A627" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C627" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D627" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E627" s="1">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="628" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A628" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C628" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D628" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E628" s="1">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="629" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A629" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C629" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D629" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E629" s="1">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="630" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A630" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C630" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D630" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E630" s="1">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="631" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A631" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C631" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D631" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E631" s="1">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="632" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A632" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C632" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D632" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E632" s="1">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="633" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A633" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C633" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D633" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E633" s="1">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="634" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A634" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C634" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D634" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E634" s="1">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="635" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A635" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C635" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D635" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E635" s="1">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="636" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A636" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B636" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C636" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D636" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E636" s="1">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="637" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A637" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C637" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D637" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E637" s="1">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="638" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A638" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C638" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D638" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E638" s="1">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="639" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A639" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C639" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D639" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E639" s="1">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="640" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A640" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B640" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C640" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D640" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E640" s="1">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="641" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A641" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B641" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C641" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D641" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E641" s="1">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="642" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A642" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B642" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C642" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D642" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E642" s="1">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="643" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A643" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C643" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D643" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E643" s="1">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A644" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C644" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D644" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E644" s="1">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="645" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A645" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B645" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C645" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D645" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E645" s="1">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A646" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C646" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D646" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E646" s="1">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A647" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B647" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C647" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D647" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E647" s="1">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="648" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A648" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C648" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D648" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E648" s="1">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="649" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A649" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B649" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C649" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D649" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E649" s="1">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="650" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A650" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B650" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C650" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D650" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E650" s="1">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="651" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A651" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B651" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C651" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D651" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E651" s="1">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="652" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A652" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C652" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D652" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E652" s="1">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="653" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A653" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B653" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C653" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D653" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E653" s="1">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="654" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A654" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C654" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D654" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E654" s="1">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="655" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A655" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B655" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C655" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D655" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E655" s="1">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="656" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A656" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C656" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D656" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E656" s="1">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="657" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A657" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B657" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C657" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D657" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E657" s="1">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="658" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A658" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B658" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C658" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D658" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E658" s="1">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="659" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A659" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C659" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D659" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E659" s="1">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="660" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A660" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B660" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C660" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D660" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E660" s="1">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="661" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A661" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C661" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D661" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E661" s="1">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="662" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A662" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C662" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D662" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E662" s="1">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="663" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A663" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C663" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D663" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E663" s="1">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="664" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A664" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C664" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D664" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E664" s="1">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="665" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A665" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C665" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D665" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E665" s="1">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="666" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A666" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C666" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D666" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E666" s="1">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="667" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A667" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C667" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D667" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E667" s="1">
+        <v>2936</v>
+      </c>
+    </row>
+    <row r="668" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A668" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C668" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D668" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E668" s="1">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="669" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A669" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C669" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D669" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E669" s="1">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="670" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A670" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C670" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D670" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E670" s="1">
+        <v>3043</v>
+      </c>
+    </row>
+    <row r="671" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A671" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C671" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D671" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E671" s="1">
+        <v>3054</v>
+      </c>
+    </row>
+    <row r="672" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A672" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C672" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D672" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E672" s="1">
+        <v>3218</v>
+      </c>
+    </row>
+    <row r="673" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A673" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C673" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D673" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E673" s="1">
+        <v>3316</v>
+      </c>
+    </row>
+    <row r="674" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A674" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C674" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D674" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E674" s="1">
+        <v>3334</v>
+      </c>
+    </row>
+    <row r="675" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A675" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C675" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D675" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E675" s="1">
+        <v>3358</v>
+      </c>
+    </row>
+    <row r="676" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A676" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C676" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D676" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E676" s="1">
+        <v>4558</v>
+      </c>
+    </row>
+    <row r="677" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A677" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C677" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D677" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E677" s="1">
+        <v>4797</v>
+      </c>
+    </row>
+    <row r="678" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A678" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C678" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D678" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E678" s="1">
+        <v>4880</v>
+      </c>
+    </row>
+    <row r="679" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A679" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C679" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D679" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E679" s="1">
+        <v>5149</v>
+      </c>
+    </row>
+    <row r="680" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A680" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C680" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D680" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E680" s="1">
+        <v>5158</v>
+      </c>
+    </row>
+    <row r="681" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A681" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C681" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D681" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E681" s="1">
+        <v>5343</v>
+      </c>
+    </row>
+    <row r="682" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A682" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C682" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D682" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E682" s="1">
+        <v>5640</v>
+      </c>
+    </row>
+    <row r="683" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A683" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C683" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D683" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E683" s="1">
+        <v>6124</v>
+      </c>
+    </row>
+    <row r="684" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A684" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C684" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D684" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E684" s="1">
+        <v>6143</v>
+      </c>
+    </row>
+    <row r="685" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A685" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C685" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D685" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E685" s="1">
+        <v>6517</v>
+      </c>
+    </row>
+    <row r="686" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A686" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B686" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C686" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D686" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E686" s="1">
+        <v>6737</v>
+      </c>
+    </row>
+    <row r="687" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A687" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C687" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D687" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E687" s="1">
+        <v>6873</v>
+      </c>
+    </row>
+    <row r="688" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A688" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B688" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C688" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D688" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E688" s="1">
+        <v>7646</v>
+      </c>
+    </row>
+    <row r="689" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A689" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C689" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D689" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E689" s="1">
+        <v>7679</v>
+      </c>
+    </row>
+    <row r="690" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A690" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B690" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C690" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D690" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E690" s="1">
+        <v>8228</v>
+      </c>
+    </row>
+    <row r="691" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A691" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C691" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D691" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E691" s="1">
+        <v>9679</v>
+      </c>
+    </row>
+    <row r="692" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A692" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C692" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D692" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E692" s="1">
+        <v>10218</v>
+      </c>
+    </row>
+    <row r="693" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A693" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C693" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D693" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E693" s="1">
+        <v>13064</v>
+      </c>
+    </row>
+    <row r="694" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A694" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C694" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D694" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E694" s="1">
+        <v>15044</v>
+      </c>
+    </row>
+    <row r="695" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A695" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C695" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D695" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E695" s="1">
+        <v>18905</v>
+      </c>
+    </row>
+    <row r="696" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A696" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C696" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D696" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E696" s="1">
+        <v>20362</v>
+      </c>
+    </row>
+    <row r="697" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A697" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C697" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D697" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E697" s="1">
+        <v>23053</v>
+      </c>
+    </row>
+    <row r="698" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A698" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C698" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D698" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E698" s="1">
+        <v>23193</v>
+      </c>
+    </row>
+    <row r="699" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A699" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C699" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D699" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E699" s="1">
+        <v>26945</v>
+      </c>
+    </row>
+    <row r="700" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A700" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C700" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D700" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E700" s="1">
+        <v>27151</v>
+      </c>
+    </row>
+    <row r="701" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A701" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C701" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D701" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E701" s="1">
+        <v>31934</v>
+      </c>
+    </row>
+    <row r="702" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A702" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C702" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D702" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E702" s="1">
+        <v>33556</v>
+      </c>
+    </row>
+    <row r="703" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A703" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B703" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C703" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D703" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E703" s="1">
+        <v>33882</v>
+      </c>
+    </row>
+    <row r="704" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A704" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B704" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C704" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D704" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E704" s="1">
+        <v>43470</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E608" xr:uid="{3D6C85BC-B3BC-48F3-9105-76B4ECBACCE9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J5:M117">
     <sortCondition ref="J5:J117"/>
   </sortState>
@@ -11229,7 +12865,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91508C2B-BB50-4B90-B35A-4928148A54F5}">
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
@@ -12304,6 +13940,187 @@
         <v>159</v>
       </c>
     </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C98" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C99" s="1">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C100" s="1">
+        <v>25250</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C101" s="1">
+        <v>2633</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C102" s="1">
+        <v>6653</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C103" s="1">
+        <v>203382</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C104" s="1">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C105" s="1">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C106" s="1">
+        <v>39072</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C107" s="1">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C108" s="1">
+        <v>202068</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C109" s="1">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C110" s="1">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C111" s="1">
+        <v>14048</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C112" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C113" s="1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C51">
     <sortCondition ref="A2:A51"/>
